--- a/1-10-2005.xlsx
+++ b/1-10-2005.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tasni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nti\graduation_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C8C82C-3116-4E76-83F5-F0B258EDBD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C887722-8F0A-4CF0-8183-8D50EDEBF5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1179,21 +1179,18 @@
         <v>10</v>
       </c>
       <c r="AK2" s="5">
-        <f t="shared" ref="AK2:AK103" si="0">AH2/AI2</f>
         <v>14</v>
       </c>
       <c r="AL2" s="8">
         <v>34</v>
       </c>
       <c r="AM2" s="5">
-        <f t="shared" ref="AM2:AM103" si="1">1.24*AK2+1.9</f>
         <v>19.259999999999998</v>
       </c>
       <c r="AN2" s="6">
         <v>1</v>
       </c>
       <c r="AO2" s="6">
-        <f t="shared" ref="AO2:AO28" si="2">4*AN2^2+10</f>
         <v>14</v>
       </c>
       <c r="AP2" s="5">
@@ -1322,21 +1319,18 @@
         <v>8</v>
       </c>
       <c r="AK3" s="5">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AL3" s="8">
         <v>33</v>
       </c>
       <c r="AM3" s="5">
-        <f t="shared" si="1"/>
         <v>18.02</v>
       </c>
       <c r="AN3" s="6">
         <v>0.4</v>
       </c>
       <c r="AO3" s="6">
-        <f t="shared" si="2"/>
         <v>10.64</v>
       </c>
       <c r="AP3" s="5">
@@ -1465,21 +1459,18 @@
         <v>12</v>
       </c>
       <c r="AK4" s="5">
-        <f t="shared" si="0"/>
         <v>14.6</v>
       </c>
       <c r="AL4" s="8">
         <v>34.5</v>
       </c>
       <c r="AM4" s="5">
-        <f t="shared" si="1"/>
         <v>20.003999999999998</v>
       </c>
       <c r="AN4" s="6">
         <v>2.8</v>
       </c>
       <c r="AO4" s="6">
-        <f t="shared" si="2"/>
         <v>41.36</v>
       </c>
       <c r="AP4" s="5">
@@ -1608,21 +1599,18 @@
         <v>13</v>
       </c>
       <c r="AK5" s="5">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AL5" s="8">
         <v>35</v>
       </c>
       <c r="AM5" s="5">
-        <f t="shared" si="1"/>
         <v>21.74</v>
       </c>
       <c r="AN5" s="6">
         <v>0.5</v>
       </c>
       <c r="AO5" s="6">
-        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="AP5" s="5">
@@ -1751,21 +1739,18 @@
         <v>14</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AL6" s="8">
         <v>36.700000000000003</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" si="1"/>
         <v>18.02</v>
       </c>
       <c r="AN6" s="6">
         <v>2.5</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="AP6" s="5">
@@ -1894,21 +1879,18 @@
         <v>8</v>
       </c>
       <c r="AK7" s="5">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL7" s="8">
         <v>35.700000000000003</v>
       </c>
       <c r="AM7" s="5">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN7" s="6">
         <v>3</v>
       </c>
       <c r="AO7" s="6">
-        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="AP7" s="5">
@@ -2037,21 +2019,18 @@
         <v>10</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
       <c r="AL8" s="8">
         <v>33</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="1"/>
         <v>19.88</v>
       </c>
       <c r="AN8" s="6">
         <v>1.5</v>
       </c>
       <c r="AO8" s="6">
-        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="AP8" s="5">
@@ -2180,21 +2159,18 @@
         <v>11</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
       <c r="AL9" s="8">
         <v>35</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" si="1"/>
         <v>23.971999999999998</v>
       </c>
       <c r="AN9" s="6">
         <v>2</v>
       </c>
       <c r="AO9" s="6">
-        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="AP9" s="5">
@@ -2323,21 +2299,18 @@
         <v>9</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AL10" s="8">
         <v>36.6</v>
       </c>
       <c r="AM10" s="5">
-        <f t="shared" si="1"/>
         <v>18.02</v>
       </c>
       <c r="AN10" s="6">
         <v>1.7</v>
       </c>
       <c r="AO10" s="6">
-        <f t="shared" si="2"/>
         <v>21.56</v>
       </c>
       <c r="AP10" s="5">
@@ -2466,21 +2439,18 @@
         <v>13</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="AL11" s="8">
         <v>36</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="1"/>
         <v>14.92</v>
       </c>
       <c r="AN11" s="6">
         <v>2.7</v>
       </c>
       <c r="AO11" s="6">
-        <f t="shared" si="2"/>
         <v>39.160000000000004</v>
       </c>
       <c r="AP11" s="5">
@@ -2609,21 +2579,18 @@
         <v>13</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="AL12" s="8">
         <v>34.799999999999997</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="1"/>
         <v>14.92</v>
       </c>
       <c r="AN12" s="6">
         <v>3.3</v>
       </c>
       <c r="AO12" s="6">
-        <f t="shared" si="2"/>
         <v>53.559999999999995</v>
       </c>
       <c r="AP12" s="5">
@@ -2752,21 +2719,18 @@
         <v>9</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="AL13" s="8">
         <v>35.5</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" si="1"/>
         <v>17.399999999999999</v>
       </c>
       <c r="AN13" s="6">
         <v>1</v>
       </c>
       <c r="AO13" s="6">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="AP13" s="5">
@@ -2895,21 +2859,18 @@
         <v>13</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="AL14" s="8">
         <v>32</v>
       </c>
       <c r="AM14" s="5">
-        <f t="shared" si="1"/>
         <v>19.259999999999998</v>
       </c>
       <c r="AN14" s="6">
         <v>0.7</v>
       </c>
       <c r="AO14" s="6">
-        <f t="shared" si="2"/>
         <v>11.959999999999999</v>
       </c>
       <c r="AP14" s="5">
@@ -3038,21 +2999,18 @@
         <v>12</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AL15" s="8">
         <v>34</v>
       </c>
       <c r="AM15" s="5">
-        <f t="shared" si="1"/>
         <v>24.22</v>
       </c>
       <c r="AN15" s="6">
         <v>1.3</v>
       </c>
       <c r="AO15" s="6">
-        <f t="shared" si="2"/>
         <v>16.760000000000002</v>
       </c>
       <c r="AP15" s="5">
@@ -3181,21 +3139,18 @@
         <v>12</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="0"/>
         <v>10.625</v>
       </c>
       <c r="AL16" s="8">
         <v>37.4</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" si="1"/>
         <v>15.075000000000001</v>
       </c>
       <c r="AN16" s="6">
         <v>2.8</v>
       </c>
       <c r="AO16" s="6">
-        <f t="shared" si="2"/>
         <v>41.36</v>
       </c>
       <c r="AP16" s="5">
@@ -3324,21 +3279,18 @@
         <v>13</v>
       </c>
       <c r="AK17" s="5">
-        <f t="shared" si="0"/>
         <v>15.8</v>
       </c>
       <c r="AL17" s="8">
         <v>32</v>
       </c>
       <c r="AM17" s="5">
-        <f t="shared" si="1"/>
         <v>21.492000000000001</v>
       </c>
       <c r="AN17" s="6">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6">
-        <f t="shared" si="2"/>
         <v>15.76</v>
       </c>
       <c r="AP17" s="5">
@@ -3467,21 +3419,18 @@
         <v>9</v>
       </c>
       <c r="AK18" s="5">
-        <f t="shared" si="0"/>
         <v>16.399999999999999</v>
       </c>
       <c r="AL18" s="8">
         <v>34.5</v>
       </c>
       <c r="AM18" s="10">
-        <f t="shared" si="1"/>
         <v>22.235999999999997</v>
       </c>
       <c r="AN18" s="6">
         <v>2.1</v>
       </c>
       <c r="AO18" s="6">
-        <f t="shared" si="2"/>
         <v>27.64</v>
       </c>
       <c r="AP18" s="5">
@@ -3610,21 +3559,18 @@
         <v>14</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
       <c r="AL19" s="8">
         <v>34</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" si="1"/>
         <v>8.7200000000000006</v>
       </c>
       <c r="AN19" s="6">
         <v>2.5</v>
       </c>
       <c r="AO19" s="6">
-        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="AP19" s="5">
@@ -3753,21 +3699,18 @@
         <v>12</v>
       </c>
       <c r="AK20" s="5">
-        <f t="shared" si="0"/>
         <v>11.75</v>
       </c>
       <c r="AL20" s="8">
         <v>33.6</v>
       </c>
       <c r="AM20" s="5">
-        <f t="shared" si="1"/>
         <v>16.47</v>
       </c>
       <c r="AN20" s="6">
         <v>3.2</v>
       </c>
       <c r="AO20" s="6">
-        <f t="shared" si="2"/>
         <v>50.960000000000008</v>
       </c>
       <c r="AP20" s="5">
@@ -3896,21 +3839,18 @@
         <v>8</v>
       </c>
       <c r="AK21" s="5">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL21" s="8">
         <v>35.700000000000003</v>
       </c>
       <c r="AM21" s="5">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN21" s="6">
         <v>2.2000000000000002</v>
       </c>
       <c r="AO21" s="6">
-        <f t="shared" si="2"/>
         <v>29.360000000000003</v>
       </c>
       <c r="AP21" s="5">
@@ -4037,21 +3977,18 @@
         <v>12</v>
       </c>
       <c r="AK22" s="5">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="AL22" s="8">
         <v>32</v>
       </c>
       <c r="AM22" s="5">
-        <f t="shared" si="1"/>
         <v>17.399999999999999</v>
       </c>
       <c r="AN22" s="6">
         <v>1.5</v>
       </c>
       <c r="AO22" s="6">
-        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="AP22" s="5">
@@ -4180,21 +4117,18 @@
         <v>12</v>
       </c>
       <c r="AK23" s="5">
-        <f t="shared" si="0"/>
         <v>15.8</v>
       </c>
       <c r="AL23" s="8">
         <v>38.5</v>
       </c>
       <c r="AM23" s="5">
-        <f t="shared" si="1"/>
         <v>21.492000000000001</v>
       </c>
       <c r="AN23" s="6">
         <v>1</v>
       </c>
       <c r="AO23" s="6">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="AP23" s="5">
@@ -4323,21 +4257,18 @@
         <v>13</v>
       </c>
       <c r="AK24" s="5">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AL24" s="8">
         <v>38</v>
       </c>
       <c r="AM24" s="5">
-        <f t="shared" si="1"/>
         <v>21.74</v>
       </c>
       <c r="AN24" s="6">
         <v>0.8</v>
       </c>
       <c r="AO24" s="6">
-        <f t="shared" si="2"/>
         <v>12.56</v>
       </c>
       <c r="AP24" s="5">
@@ -4466,21 +4397,18 @@
         <v>12</v>
       </c>
       <c r="AK25" s="5">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL25" s="8">
         <v>35</v>
       </c>
       <c r="AM25" s="5">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN25" s="6">
         <v>2.8</v>
       </c>
       <c r="AO25" s="6">
-        <f t="shared" si="2"/>
         <v>41.36</v>
       </c>
       <c r="AP25" s="5">
@@ -4609,21 +4537,18 @@
         <v>13</v>
       </c>
       <c r="AK26" s="11">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AL26" s="12">
         <v>34</v>
       </c>
       <c r="AM26" s="11">
-        <f t="shared" si="1"/>
         <v>27.939999999999998</v>
       </c>
       <c r="AN26" s="6">
         <v>2.2999999999999998</v>
       </c>
       <c r="AO26" s="13">
-        <f t="shared" si="2"/>
         <v>31.159999999999997</v>
       </c>
       <c r="AP26" s="5">
@@ -4752,21 +4677,18 @@
         <v>9</v>
       </c>
       <c r="AK27" s="11">
-        <f t="shared" si="0"/>
         <v>19.399999999999999</v>
       </c>
       <c r="AL27" s="12">
         <v>34</v>
       </c>
       <c r="AM27" s="11">
-        <f t="shared" si="1"/>
         <v>25.955999999999996</v>
       </c>
       <c r="AN27" s="6">
         <v>1.5</v>
       </c>
       <c r="AO27" s="13">
-        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="AP27" s="5">
@@ -4895,21 +4817,18 @@
         <v>9</v>
       </c>
       <c r="AK28" s="11">
-        <f t="shared" si="0"/>
         <v>11.571428571428571</v>
       </c>
       <c r="AL28" s="12">
         <v>39</v>
       </c>
       <c r="AM28" s="11">
-        <f t="shared" si="1"/>
         <v>16.248571428571427</v>
       </c>
       <c r="AN28" s="6">
         <v>1.9</v>
       </c>
       <c r="AO28" s="13">
-        <f t="shared" si="2"/>
         <v>24.439999999999998</v>
       </c>
       <c r="AP28" s="5">
@@ -5038,21 +4957,18 @@
         <v>13</v>
       </c>
       <c r="AK29" s="11">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL29" s="12">
         <v>37</v>
       </c>
       <c r="AM29" s="11">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN29" s="6">
         <v>2.7</v>
       </c>
       <c r="AO29" s="13">
-        <f t="shared" ref="AO29:AO30" si="3">4*AN29^2+15</f>
         <v>44.160000000000004</v>
       </c>
       <c r="AP29" s="5">
@@ -5181,21 +5097,18 @@
         <v>9</v>
       </c>
       <c r="AK30" s="11">
-        <f t="shared" si="0"/>
         <v>8.125</v>
       </c>
       <c r="AL30" s="12">
         <v>37</v>
       </c>
       <c r="AM30" s="11">
-        <f t="shared" si="1"/>
         <v>11.975</v>
       </c>
       <c r="AN30" s="6">
         <v>1.5</v>
       </c>
       <c r="AO30" s="13">
-        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="AP30" s="5">
@@ -5324,21 +5237,18 @@
         <v>10</v>
       </c>
       <c r="AK31" s="11">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AL31" s="12">
         <v>34</v>
       </c>
       <c r="AM31" s="11">
-        <f t="shared" si="1"/>
         <v>26.7</v>
       </c>
       <c r="AN31" s="6">
         <v>2.2999999999999998</v>
       </c>
       <c r="AO31" s="13">
-        <f t="shared" ref="AO31:AO37" si="4">4*AN31^2+10</f>
         <v>31.159999999999997</v>
       </c>
       <c r="AP31" s="5">
@@ -5467,21 +5377,18 @@
         <v>12</v>
       </c>
       <c r="AK32" s="11">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AL32" s="12">
         <v>38</v>
       </c>
       <c r="AM32" s="11">
-        <f t="shared" si="1"/>
         <v>29.18</v>
       </c>
       <c r="AN32" s="6">
         <v>3.5</v>
       </c>
       <c r="AO32" s="13">
-        <f t="shared" si="4"/>
         <v>59</v>
       </c>
       <c r="AP32" s="5">
@@ -5610,21 +5517,18 @@
         <v>13</v>
       </c>
       <c r="AK33" s="11">
-        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
       <c r="AL33" s="12">
         <v>35</v>
       </c>
       <c r="AM33" s="11">
-        <f t="shared" si="1"/>
         <v>13.68</v>
       </c>
       <c r="AN33" s="6">
         <v>2.1</v>
       </c>
       <c r="AO33" s="13">
-        <f t="shared" si="4"/>
         <v>27.64</v>
       </c>
       <c r="AP33" s="5">
@@ -5753,21 +5657,18 @@
         <v>11</v>
       </c>
       <c r="AK34" s="11">
-        <f t="shared" si="0"/>
         <v>8.125</v>
       </c>
       <c r="AL34" s="12">
         <v>36</v>
       </c>
       <c r="AM34" s="11">
-        <f t="shared" si="1"/>
         <v>11.975</v>
       </c>
       <c r="AN34" s="6">
         <v>2.5</v>
       </c>
       <c r="AO34" s="13">
-        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="AP34" s="5">
@@ -5896,21 +5797,18 @@
         <v>11</v>
       </c>
       <c r="AK35" s="11">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="AL35" s="12">
         <v>30</v>
       </c>
       <c r="AM35" s="11">
-        <f t="shared" si="1"/>
         <v>14.3</v>
       </c>
       <c r="AN35" s="6">
         <v>1.9</v>
       </c>
       <c r="AO35" s="13">
-        <f t="shared" si="4"/>
         <v>24.439999999999998</v>
       </c>
       <c r="AP35" s="5">
@@ -6039,21 +5937,18 @@
         <v>9</v>
       </c>
       <c r="AK36" s="11">
-        <f t="shared" si="0"/>
         <v>17.166666666666668</v>
       </c>
       <c r="AL36" s="12">
         <v>32</v>
       </c>
       <c r="AM36" s="11">
-        <f t="shared" si="1"/>
         <v>23.186666666666667</v>
       </c>
       <c r="AN36" s="6">
         <v>1.4</v>
       </c>
       <c r="AO36" s="13">
-        <f t="shared" si="4"/>
         <v>17.84</v>
       </c>
       <c r="AP36" s="5">
@@ -6182,21 +6077,18 @@
         <v>9</v>
       </c>
       <c r="AK37" s="11">
-        <f t="shared" si="0"/>
         <v>12.428571428571429</v>
       </c>
       <c r="AL37" s="12">
         <v>39</v>
       </c>
       <c r="AM37" s="11">
-        <f t="shared" si="1"/>
         <v>17.311428571428571</v>
       </c>
       <c r="AN37" s="6">
         <v>2.8</v>
       </c>
       <c r="AO37" s="13">
-        <f t="shared" si="4"/>
         <v>41.36</v>
       </c>
       <c r="AP37" s="5">
@@ -6325,21 +6217,18 @@
         <v>14</v>
       </c>
       <c r="AK38" s="11">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="AL38" s="12">
         <v>37</v>
       </c>
       <c r="AM38" s="11">
-        <f t="shared" si="1"/>
         <v>17.399999999999999</v>
       </c>
       <c r="AN38" s="6">
         <v>3.7</v>
       </c>
       <c r="AO38" s="13">
-        <f>4*AN38^2+5</f>
         <v>59.760000000000005</v>
       </c>
       <c r="AP38" s="5">
@@ -6468,21 +6357,18 @@
         <v>8</v>
       </c>
       <c r="AK39" s="11">
-        <f t="shared" si="0"/>
         <v>19.8</v>
       </c>
       <c r="AL39" s="12">
         <v>38</v>
       </c>
       <c r="AM39" s="11">
-        <f t="shared" si="1"/>
         <v>26.451999999999998</v>
       </c>
       <c r="AN39" s="6">
         <v>2.5</v>
       </c>
       <c r="AO39" s="13">
-        <f t="shared" ref="AO39:AO41" si="5">4*AN39^2+10</f>
         <v>35</v>
       </c>
       <c r="AP39" s="5">
@@ -6611,21 +6497,18 @@
         <v>9</v>
       </c>
       <c r="AK40" s="11">
-        <f t="shared" si="0"/>
         <v>13.166666666666666</v>
       </c>
       <c r="AL40" s="12">
         <v>33</v>
       </c>
       <c r="AM40" s="11">
-        <f t="shared" si="1"/>
         <v>18.226666666666663</v>
       </c>
       <c r="AN40" s="6">
         <v>2.1</v>
       </c>
       <c r="AO40" s="13">
-        <f t="shared" si="5"/>
         <v>27.64</v>
       </c>
       <c r="AP40" s="5">
@@ -6754,21 +6637,18 @@
         <v>12</v>
       </c>
       <c r="AK41" s="11">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="AL41" s="12">
         <v>34</v>
       </c>
       <c r="AM41" s="11">
-        <f t="shared" si="1"/>
         <v>14.3</v>
       </c>
       <c r="AN41" s="6">
         <v>1.7</v>
       </c>
       <c r="AO41" s="13">
-        <f t="shared" si="5"/>
         <v>21.56</v>
       </c>
       <c r="AP41" s="5">
@@ -6897,21 +6777,18 @@
         <v>11</v>
       </c>
       <c r="AK42" s="11">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AL42" s="12">
         <v>37</v>
       </c>
       <c r="AM42" s="11">
-        <f t="shared" si="1"/>
         <v>29.18</v>
       </c>
       <c r="AN42" s="6">
         <v>3.5</v>
       </c>
       <c r="AO42" s="13">
-        <f>4*AN42^2+5</f>
         <v>54</v>
       </c>
       <c r="AP42" s="5">
@@ -7040,21 +6917,18 @@
         <v>13</v>
       </c>
       <c r="AK43" s="11">
-        <f t="shared" si="0"/>
         <v>9.375</v>
       </c>
       <c r="AL43" s="12">
         <v>39</v>
       </c>
       <c r="AM43" s="11">
-        <f t="shared" si="1"/>
         <v>13.525</v>
       </c>
       <c r="AN43" s="6">
         <v>1.4</v>
       </c>
       <c r="AO43" s="13">
-        <f t="shared" ref="AO43:AO46" si="6">4*AN43^2+10</f>
         <v>17.84</v>
       </c>
       <c r="AP43" s="5">
@@ -7183,21 +7057,18 @@
         <v>14</v>
       </c>
       <c r="AK44" s="11">
-        <f t="shared" si="0"/>
         <v>9.7142857142857135</v>
       </c>
       <c r="AL44" s="12">
         <v>39</v>
       </c>
       <c r="AM44" s="11">
-        <f t="shared" si="1"/>
         <v>13.945714285714285</v>
       </c>
       <c r="AN44" s="6">
         <v>1.9</v>
       </c>
       <c r="AO44" s="13">
-        <f t="shared" si="6"/>
         <v>24.439999999999998</v>
       </c>
       <c r="AP44" s="5">
@@ -7326,21 +7197,18 @@
         <v>8</v>
       </c>
       <c r="AK45" s="11">
-        <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
       <c r="AL45" s="12">
         <v>37</v>
       </c>
       <c r="AM45" s="11">
-        <f t="shared" si="1"/>
         <v>19.569999999999997</v>
       </c>
       <c r="AN45" s="6">
         <v>2.4</v>
       </c>
       <c r="AO45" s="13">
-        <f t="shared" si="6"/>
         <v>33.04</v>
       </c>
       <c r="AP45" s="5">
@@ -7469,21 +7337,18 @@
         <v>11</v>
       </c>
       <c r="AK46" s="11">
-        <f t="shared" si="0"/>
         <v>14.375</v>
       </c>
       <c r="AL46" s="12">
         <v>40</v>
       </c>
       <c r="AM46" s="11">
-        <f t="shared" si="1"/>
         <v>19.724999999999998</v>
       </c>
       <c r="AN46" s="6">
         <v>2.5</v>
       </c>
       <c r="AO46" s="13">
-        <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="AP46" s="5">
@@ -7612,21 +7477,18 @@
         <v>9</v>
       </c>
       <c r="AK47" s="11">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AL47" s="12">
         <v>33</v>
       </c>
       <c r="AM47" s="11">
-        <f t="shared" si="1"/>
         <v>26.7</v>
       </c>
       <c r="AN47" s="6">
         <v>3.1</v>
       </c>
       <c r="AO47" s="13">
-        <f>4*AN47^2+15</f>
         <v>53.440000000000005</v>
       </c>
       <c r="AP47" s="5">
@@ -7755,21 +7617,18 @@
         <v>10</v>
       </c>
       <c r="AK48" s="11">
-        <f t="shared" si="0"/>
         <v>13.666666666666666</v>
       </c>
       <c r="AL48" s="12">
         <v>35</v>
       </c>
       <c r="AM48" s="11">
-        <f t="shared" si="1"/>
         <v>18.846666666666664</v>
       </c>
       <c r="AN48" s="6">
         <v>2.8</v>
       </c>
       <c r="AO48" s="13">
-        <f t="shared" ref="AO48:AO75" si="7">4*AN48^2+10</f>
         <v>41.36</v>
       </c>
       <c r="AP48" s="5">
@@ -7898,21 +7757,18 @@
         <v>13</v>
       </c>
       <c r="AK49" s="11">
-        <f t="shared" si="0"/>
         <v>13.571428571428571</v>
       </c>
       <c r="AL49" s="12">
         <v>36</v>
       </c>
       <c r="AM49" s="11">
-        <f t="shared" si="1"/>
         <v>18.728571428571428</v>
       </c>
       <c r="AN49" s="6">
         <v>1.9</v>
       </c>
       <c r="AO49" s="13">
-        <f t="shared" si="7"/>
         <v>24.439999999999998</v>
       </c>
       <c r="AP49" s="5">
@@ -8041,21 +7897,18 @@
         <v>14</v>
       </c>
       <c r="AK50" s="11">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL50" s="12">
         <v>33</v>
       </c>
       <c r="AM50" s="11">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN50" s="6">
         <v>1.7</v>
       </c>
       <c r="AO50" s="13">
-        <f t="shared" si="7"/>
         <v>21.56</v>
       </c>
       <c r="AP50" s="5">
@@ -8184,21 +8037,18 @@
         <v>14</v>
       </c>
       <c r="AK51" s="13">
-        <f t="shared" si="0"/>
         <v>16.399999999999999</v>
       </c>
       <c r="AL51" s="12">
         <v>38.724386280657903</v>
       </c>
       <c r="AM51" s="13">
-        <f t="shared" si="1"/>
         <v>22.235999999999997</v>
       </c>
       <c r="AN51" s="13">
         <v>2.4796184238962109</v>
       </c>
       <c r="AO51" s="13">
-        <f t="shared" si="7"/>
         <v>34.594030112502118</v>
       </c>
       <c r="AP51" s="5">
@@ -8327,21 +8177,18 @@
         <v>14</v>
       </c>
       <c r="AK52" s="13">
-        <f t="shared" si="0"/>
         <v>14.2</v>
       </c>
       <c r="AL52" s="12">
         <v>40.615620723058584</v>
       </c>
       <c r="AM52" s="13">
-        <f t="shared" si="1"/>
         <v>19.507999999999999</v>
       </c>
       <c r="AN52" s="13">
         <v>3.1385033985634379</v>
       </c>
       <c r="AO52" s="13">
-        <f t="shared" si="7"/>
         <v>49.400814331176996</v>
       </c>
       <c r="AP52" s="5">
@@ -8470,21 +8317,18 @@
         <v>11</v>
       </c>
       <c r="AK53" s="13">
-        <f t="shared" si="0"/>
         <v>16.571428571428573</v>
       </c>
       <c r="AL53" s="12">
         <v>43.576570055161874</v>
       </c>
       <c r="AM53" s="13">
-        <f t="shared" si="1"/>
         <v>22.44857142857143</v>
       </c>
       <c r="AN53" s="13">
         <v>2.9155793279237248</v>
       </c>
       <c r="AO53" s="13">
-        <f t="shared" si="7"/>
         <v>44.002411269664634</v>
       </c>
       <c r="AP53" s="5">
@@ -8613,21 +8457,18 @@
         <v>11</v>
       </c>
       <c r="AK54" s="13">
-        <f t="shared" si="0"/>
         <v>13.142857142857142</v>
       </c>
       <c r="AL54" s="12">
         <v>42.716607721241786</v>
       </c>
       <c r="AM54" s="13">
-        <f t="shared" si="1"/>
         <v>18.197142857142854</v>
       </c>
       <c r="AN54" s="13">
         <v>3.0390446636671946</v>
       </c>
       <c r="AO54" s="13">
-        <f t="shared" si="7"/>
         <v>46.943169871056206</v>
       </c>
       <c r="AP54" s="5">
@@ -8756,21 +8597,18 @@
         <v>8</v>
       </c>
       <c r="AK55" s="13">
-        <f t="shared" si="0"/>
         <v>13.857142857142858</v>
       </c>
       <c r="AL55" s="12">
         <v>41.174300547607118</v>
       </c>
       <c r="AM55" s="13">
-        <f t="shared" si="1"/>
         <v>19.082857142857144</v>
       </c>
       <c r="AN55" s="13">
         <v>1.9230375362379737</v>
       </c>
       <c r="AO55" s="13">
-        <f t="shared" si="7"/>
         <v>24.792293463120863</v>
       </c>
       <c r="AP55" s="5">
@@ -8899,21 +8737,18 @@
         <v>13</v>
       </c>
       <c r="AK56" s="13">
-        <f t="shared" si="0"/>
         <v>14.428571428571429</v>
       </c>
       <c r="AL56" s="12">
         <v>37.915942055244216</v>
       </c>
       <c r="AM56" s="13">
-        <f t="shared" si="1"/>
         <v>19.791428571428572</v>
       </c>
       <c r="AN56" s="13">
         <v>3.123366957853615</v>
       </c>
       <c r="AO56" s="13">
-        <f t="shared" si="7"/>
         <v>49.021684613646983</v>
       </c>
       <c r="AP56" s="5">
@@ -9042,21 +8877,18 @@
         <v>9</v>
       </c>
       <c r="AK57" s="13">
-        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
       <c r="AL57" s="12">
         <v>40.305835141097802</v>
       </c>
       <c r="AM57" s="13">
-        <f t="shared" si="1"/>
         <v>18.639999999999997</v>
       </c>
       <c r="AN57" s="13">
         <v>2.2520113713145098</v>
       </c>
       <c r="AO57" s="13">
-        <f t="shared" si="7"/>
         <v>30.286220866119436</v>
       </c>
       <c r="AP57" s="5">
@@ -9185,21 +9017,18 @@
         <v>12</v>
       </c>
       <c r="AK58" s="13">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AL58" s="12">
         <v>41.619434297975651</v>
       </c>
       <c r="AM58" s="13">
-        <f t="shared" si="1"/>
         <v>24.22</v>
       </c>
       <c r="AN58" s="13">
         <v>2.074394032123517</v>
       </c>
       <c r="AO58" s="13">
-        <f t="shared" si="7"/>
         <v>27.212442402038651</v>
       </c>
       <c r="AP58" s="5">
@@ -9328,21 +9157,18 @@
         <v>11</v>
       </c>
       <c r="AK59" s="13">
-        <f t="shared" si="0"/>
         <v>15.6</v>
       </c>
       <c r="AL59" s="12">
         <v>39.667671005263749</v>
       </c>
       <c r="AM59" s="13">
-        <f t="shared" si="1"/>
         <v>21.244</v>
       </c>
       <c r="AN59" s="13">
         <v>2.9272095424527751</v>
       </c>
       <c r="AO59" s="13">
-        <f t="shared" si="7"/>
         <v>44.274222821706338</v>
       </c>
       <c r="AP59" s="5">
@@ -9471,21 +9297,18 @@
         <v>12</v>
       </c>
       <c r="AK60" s="13">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL60" s="12">
         <v>43.648554584222239</v>
       </c>
       <c r="AM60" s="13">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN60" s="13">
         <v>2.7303935864154623</v>
       </c>
       <c r="AO60" s="13">
-        <f t="shared" si="7"/>
         <v>39.820196546954762</v>
       </c>
       <c r="AP60" s="5">
@@ -9614,21 +9437,18 @@
         <v>10</v>
       </c>
       <c r="AK61" s="13">
-        <f t="shared" si="0"/>
         <v>17.600000000000001</v>
       </c>
       <c r="AL61" s="12">
         <v>37.159775090479165</v>
       </c>
       <c r="AM61" s="13">
-        <f t="shared" si="1"/>
         <v>23.724</v>
       </c>
       <c r="AN61" s="13">
         <v>2.1774247628499381</v>
       </c>
       <c r="AO61" s="13">
-        <f t="shared" si="7"/>
         <v>28.964714391488439</v>
       </c>
       <c r="AP61" s="5">
@@ -9757,21 +9577,18 @@
         <v>12</v>
       </c>
       <c r="AK62" s="13">
-        <f t="shared" si="0"/>
         <v>18.571428571428573</v>
       </c>
       <c r="AL62" s="12">
         <v>42.340309838035317</v>
       </c>
       <c r="AM62" s="13">
-        <f t="shared" si="1"/>
         <v>24.928571428571431</v>
       </c>
       <c r="AN62" s="13">
         <v>2.7275920043861008</v>
       </c>
       <c r="AO62" s="13">
-        <f t="shared" si="7"/>
         <v>39.759032569563949</v>
       </c>
       <c r="AP62" s="5">
@@ -9900,21 +9717,18 @@
         <v>12</v>
       </c>
       <c r="AK63" s="13">
-        <f t="shared" si="0"/>
         <v>20.399999999999999</v>
       </c>
       <c r="AL63" s="12">
         <v>38.212328198938295</v>
       </c>
       <c r="AM63" s="13">
-        <f t="shared" si="1"/>
         <v>27.195999999999998</v>
       </c>
       <c r="AN63" s="13">
         <v>1.7628440908119598</v>
       </c>
       <c r="AO63" s="13">
-        <f t="shared" si="7"/>
         <v>22.430477154042581</v>
       </c>
       <c r="AP63" s="5">
@@ -10043,21 +9857,18 @@
         <v>8</v>
       </c>
       <c r="AK64" s="13">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AL64" s="12">
         <v>43.333349912562177</v>
       </c>
       <c r="AM64" s="13">
-        <f t="shared" si="1"/>
         <v>21.74</v>
       </c>
       <c r="AN64" s="13">
         <v>3.6549383253788008</v>
       </c>
       <c r="AO64" s="13">
-        <f t="shared" si="7"/>
         <v>63.43429664929117</v>
       </c>
       <c r="AP64" s="5">
@@ -10186,21 +9997,18 @@
         <v>8</v>
       </c>
       <c r="AK65" s="13">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AL65" s="12">
         <v>37.609530567069058</v>
       </c>
       <c r="AM65" s="13">
-        <f t="shared" si="1"/>
         <v>26.7</v>
       </c>
       <c r="AN65" s="13">
         <v>2.0983183705350994</v>
       </c>
       <c r="AO65" s="13">
-        <f t="shared" si="7"/>
         <v>27.611759936500299</v>
       </c>
       <c r="AP65" s="5">
@@ -10329,21 +10137,18 @@
         <v>13</v>
       </c>
       <c r="AK66" s="13">
-        <f t="shared" si="0"/>
         <v>13.833333333333334</v>
       </c>
       <c r="AL66" s="12">
         <v>41.352590341829675</v>
       </c>
       <c r="AM66" s="13">
-        <f t="shared" si="1"/>
         <v>19.053333333333331</v>
       </c>
       <c r="AN66" s="13">
         <v>2.0702707614587812</v>
       </c>
       <c r="AO66" s="13">
-        <f t="shared" si="7"/>
         <v>27.144084103004488</v>
       </c>
       <c r="AP66" s="5">
@@ -10472,21 +10277,18 @@
         <v>12</v>
       </c>
       <c r="AK67" s="13">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL67" s="12">
         <v>43.272775624854596</v>
       </c>
       <c r="AM67" s="13">
-        <f t="shared" si="1"/>
         <v>20.5</v>
       </c>
       <c r="AN67" s="13">
         <v>2.998706527346779</v>
       </c>
       <c r="AO67" s="13">
-        <f t="shared" si="7"/>
         <v>45.968963348608717</v>
       </c>
       <c r="AP67" s="5">
@@ -10615,21 +10417,18 @@
         <v>11</v>
       </c>
       <c r="AK68" s="13">
-        <f t="shared" si="0"/>
         <v>20.333333333333332</v>
       </c>
       <c r="AL68" s="12">
         <v>42.794318668482774</v>
       </c>
       <c r="AM68" s="13">
-        <f t="shared" si="1"/>
         <v>27.11333333333333</v>
       </c>
       <c r="AN68" s="13">
         <v>1.631231999792834</v>
       </c>
       <c r="AO68" s="13">
-        <f t="shared" si="7"/>
         <v>20.643671348592513</v>
       </c>
       <c r="AP68" s="5">
@@ -10758,21 +10557,18 @@
         <v>8</v>
       </c>
       <c r="AK69" s="13">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AL69" s="12">
         <v>40.92582088770024</v>
       </c>
       <c r="AM69" s="13">
-        <f t="shared" si="1"/>
         <v>22.979999999999997</v>
       </c>
       <c r="AN69" s="13">
         <v>3.6434421646050552</v>
       </c>
       <c r="AO69" s="13">
-        <f t="shared" si="7"/>
         <v>63.098683227287879</v>
       </c>
       <c r="AP69" s="5">
@@ -10901,21 +10697,18 @@
         <v>14</v>
       </c>
       <c r="AK70" s="13">
-        <f t="shared" si="0"/>
         <v>18.8</v>
       </c>
       <c r="AL70" s="12">
         <v>40.757919500931564</v>
       </c>
       <c r="AM70" s="13">
-        <f t="shared" si="1"/>
         <v>25.212</v>
       </c>
       <c r="AN70" s="13">
         <v>3.1616481506723675</v>
       </c>
       <c r="AO70" s="13">
-        <f t="shared" si="7"/>
         <v>49.984076114600008</v>
       </c>
       <c r="AP70" s="5">
@@ -11044,21 +10837,18 @@
         <v>9</v>
       </c>
       <c r="AK71" s="13">
-        <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
       <c r="AL71" s="12">
         <v>36.84862500780207</v>
       </c>
       <c r="AM71" s="13">
-        <f t="shared" si="1"/>
         <v>22.566666666666666</v>
       </c>
       <c r="AN71" s="13">
         <v>3.0285511344665808</v>
       </c>
       <c r="AO71" s="13">
-        <f t="shared" si="7"/>
         <v>46.688487896315252</v>
       </c>
       <c r="AP71" s="5">
@@ -11187,21 +10977,18 @@
         <v>11</v>
       </c>
       <c r="AK72" s="13">
-        <f t="shared" si="0"/>
         <v>18.2</v>
       </c>
       <c r="AL72" s="12">
         <v>43.023652821110971</v>
       </c>
       <c r="AM72" s="13">
-        <f t="shared" si="1"/>
         <v>24.467999999999996</v>
       </c>
       <c r="AN72" s="13">
         <v>2.9612525099148068</v>
       </c>
       <c r="AO72" s="13">
-        <f t="shared" si="7"/>
         <v>45.07606570990697</v>
       </c>
       <c r="AP72" s="5">
@@ -11330,21 +11117,18 @@
         <v>12</v>
       </c>
       <c r="AK73" s="13">
-        <f t="shared" si="0"/>
         <v>14.8</v>
       </c>
       <c r="AL73" s="12">
         <v>37.966010594202395</v>
       </c>
       <c r="AM73" s="13">
-        <f t="shared" si="1"/>
         <v>20.251999999999999</v>
       </c>
       <c r="AN73" s="13">
         <v>2.3448548286492823</v>
       </c>
       <c r="AO73" s="13">
-        <f t="shared" si="7"/>
         <v>31.993376669759421</v>
       </c>
       <c r="AP73" s="5">
@@ -11473,21 +11257,18 @@
         <v>14</v>
       </c>
       <c r="AK74" s="13">
-        <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
       <c r="AL74" s="12">
         <v>36.128029798689731</v>
       </c>
       <c r="AM74" s="13">
-        <f t="shared" si="1"/>
         <v>20.913333333333334</v>
       </c>
       <c r="AN74" s="13">
         <v>2.1401403037014131</v>
       </c>
       <c r="AO74" s="13">
-        <f t="shared" si="7"/>
         <v>28.320802078108706</v>
       </c>
       <c r="AP74" s="5">
@@ -11616,21 +11397,18 @@
         <v>8</v>
       </c>
       <c r="AK75" s="13">
-        <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
       <c r="AL75" s="12">
         <v>36.257146123285636</v>
       </c>
       <c r="AM75" s="13">
-        <f t="shared" si="1"/>
         <v>22.566666666666666</v>
       </c>
       <c r="AN75" s="13">
         <v>3.3151471703767048</v>
       </c>
       <c r="AO75" s="13">
-        <f t="shared" si="7"/>
         <v>53.960803045026694</v>
       </c>
       <c r="AP75" s="5">
@@ -11760,21 +11538,18 @@
         <v>10</v>
       </c>
       <c r="AK76" s="16">
-        <f t="shared" si="0"/>
         <v>9.1111111111111107</v>
       </c>
       <c r="AL76" s="12">
         <v>38</v>
       </c>
       <c r="AM76" s="16">
-        <f t="shared" si="1"/>
         <v>13.197777777777777</v>
       </c>
       <c r="AN76" s="5">
         <v>1.9</v>
       </c>
       <c r="AO76" s="5">
-        <f t="shared" ref="AO76:AO80" si="8">4*AN76*AN76+10</f>
         <v>24.439999999999998</v>
       </c>
       <c r="AP76" s="5">
@@ -11903,21 +11678,18 @@
         <v>10</v>
       </c>
       <c r="AK77" s="16">
-        <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
       <c r="AL77" s="12">
         <v>43</v>
       </c>
       <c r="AM77" s="16">
-        <f t="shared" si="1"/>
         <v>22.566666666666666</v>
       </c>
       <c r="AN77" s="5">
         <v>2.1</v>
       </c>
       <c r="AO77" s="5">
-        <f t="shared" si="8"/>
         <v>27.64</v>
       </c>
       <c r="AP77" s="5">
@@ -12046,21 +11818,18 @@
         <v>14</v>
       </c>
       <c r="AK78" s="16">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AL78" s="12">
         <v>39</v>
       </c>
       <c r="AM78" s="16">
-        <f t="shared" si="1"/>
         <v>24.22</v>
       </c>
       <c r="AN78" s="5">
         <v>3.7</v>
       </c>
       <c r="AO78" s="5">
-        <f t="shared" si="8"/>
         <v>64.760000000000005</v>
       </c>
       <c r="AP78" s="5">
@@ -12189,21 +11958,18 @@
         <v>12</v>
       </c>
       <c r="AK79" s="16">
-        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="AL79" s="12">
         <v>40</v>
       </c>
       <c r="AM79" s="16">
-        <f t="shared" si="1"/>
         <v>34.14</v>
       </c>
       <c r="AN79" s="5">
         <v>1.6</v>
       </c>
       <c r="AO79" s="5">
-        <f t="shared" si="8"/>
         <v>20.240000000000002</v>
       </c>
       <c r="AP79" s="5">
@@ -12332,21 +12098,18 @@
         <v>12</v>
       </c>
       <c r="AK80" s="16">
-        <f t="shared" si="0"/>
         <v>10.333333333333334</v>
       </c>
       <c r="AL80" s="12">
         <v>38</v>
       </c>
       <c r="AM80" s="16">
-        <f t="shared" si="1"/>
         <v>14.713333333333335</v>
       </c>
       <c r="AN80" s="5">
         <v>2</v>
       </c>
       <c r="AO80" s="5">
-        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="AP80" s="5">
@@ -12475,21 +12238,18 @@
         <v>13</v>
       </c>
       <c r="AK81" s="16">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AL81" s="12">
         <v>37</v>
       </c>
       <c r="AM81" s="16">
-        <f t="shared" si="1"/>
         <v>26.7</v>
       </c>
       <c r="AN81" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="AO81" s="5">
-        <f t="shared" ref="AO81:AO82" si="9">4*AN81*AN81+15</f>
         <v>19.84</v>
       </c>
       <c r="AP81" s="5">
@@ -12618,21 +12378,18 @@
         <v>12</v>
       </c>
       <c r="AK82" s="16">
-        <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="AL82" s="12">
         <v>35</v>
       </c>
       <c r="AM82" s="16">
-        <f t="shared" si="1"/>
         <v>8.7888888888888879</v>
       </c>
       <c r="AN82" s="5">
         <v>2.1</v>
       </c>
       <c r="AO82" s="5">
-        <f t="shared" si="9"/>
         <v>32.64</v>
       </c>
       <c r="AP82" s="5">
@@ -12761,21 +12518,18 @@
         <v>12</v>
       </c>
       <c r="AK83" s="16">
-        <f t="shared" si="0"/>
         <v>16.714285714285715</v>
       </c>
       <c r="AL83" s="12">
         <v>37</v>
       </c>
       <c r="AM83" s="16">
-        <f t="shared" si="1"/>
         <v>22.625714285714285</v>
       </c>
       <c r="AN83" s="5">
         <v>0.9</v>
       </c>
       <c r="AO83" s="5">
-        <f t="shared" ref="AO83:AO86" si="10">4*AN83*AN83+10</f>
         <v>13.24</v>
       </c>
       <c r="AP83" s="5">
@@ -12904,21 +12658,18 @@
         <v>10</v>
       </c>
       <c r="AK84" s="16">
-        <f t="shared" si="0"/>
         <v>18.833333333333332</v>
       </c>
       <c r="AL84" s="12">
         <v>41</v>
       </c>
       <c r="AM84" s="16">
-        <f t="shared" si="1"/>
         <v>25.25333333333333</v>
       </c>
       <c r="AN84" s="5">
         <v>0.6</v>
       </c>
       <c r="AO84" s="5">
-        <f t="shared" si="10"/>
         <v>11.44</v>
       </c>
       <c r="AP84" s="5">
@@ -13047,21 +12798,18 @@
         <v>9</v>
       </c>
       <c r="AK85" s="16">
-        <f t="shared" si="0"/>
         <v>9.4444444444444446</v>
       </c>
       <c r="AL85" s="12">
         <v>35</v>
       </c>
       <c r="AM85" s="16">
-        <f t="shared" si="1"/>
         <v>13.611111111111112</v>
       </c>
       <c r="AN85" s="5">
         <v>1.6</v>
       </c>
       <c r="AO85" s="5">
-        <f t="shared" si="10"/>
         <v>20.240000000000002</v>
       </c>
       <c r="AP85" s="5">
@@ -13190,21 +12938,18 @@
         <v>14</v>
       </c>
       <c r="AK86" s="16">
-        <f t="shared" si="0"/>
         <v>15.833333333333334</v>
       </c>
       <c r="AL86" s="12">
         <v>34</v>
       </c>
       <c r="AM86" s="16">
-        <f t="shared" si="1"/>
         <v>21.533333333333331</v>
       </c>
       <c r="AN86" s="5">
         <v>2.5</v>
       </c>
       <c r="AO86" s="5">
-        <f t="shared" si="10"/>
         <v>35</v>
       </c>
       <c r="AP86" s="5">
@@ -13333,21 +13078,18 @@
         <v>8</v>
       </c>
       <c r="AK87" s="16">
-        <f t="shared" si="0"/>
         <v>12.222222222222221</v>
       </c>
       <c r="AL87" s="12">
         <v>36</v>
       </c>
       <c r="AM87" s="16">
-        <f t="shared" si="1"/>
         <v>17.055555555555554</v>
       </c>
       <c r="AN87" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="AO87" s="5">
-        <f>4*AN87*AN87+20</f>
         <v>24.84</v>
       </c>
       <c r="AP87" s="5">
@@ -13476,21 +13218,18 @@
         <v>12</v>
       </c>
       <c r="AK88" s="16">
-        <f t="shared" si="0"/>
         <v>12.857142857142858</v>
       </c>
       <c r="AL88" s="12">
         <v>34</v>
       </c>
       <c r="AM88" s="16">
-        <f t="shared" si="1"/>
         <v>17.842857142857142</v>
       </c>
       <c r="AN88" s="5">
         <v>1.2</v>
       </c>
       <c r="AO88" s="5">
-        <f t="shared" ref="AO88:AO91" si="11">4*AN88*AN88+10</f>
         <v>15.76</v>
       </c>
       <c r="AP88" s="5">
@@ -13619,21 +13358,18 @@
         <v>8</v>
       </c>
       <c r="AK89" s="16">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AL89" s="12">
         <v>32</v>
       </c>
       <c r="AM89" s="16">
-        <f t="shared" si="1"/>
         <v>21.74</v>
       </c>
       <c r="AN89" s="5">
         <v>2.2999999999999998</v>
       </c>
       <c r="AO89" s="5">
-        <f t="shared" si="11"/>
         <v>31.159999999999997</v>
       </c>
       <c r="AP89" s="5">
@@ -13762,21 +13498,18 @@
         <v>11</v>
       </c>
       <c r="AK90" s="16">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="AL90" s="12">
         <v>36</v>
       </c>
       <c r="AM90" s="16">
-        <f t="shared" si="1"/>
         <v>10.58</v>
       </c>
       <c r="AN90" s="5">
         <v>1.8</v>
       </c>
       <c r="AO90" s="5">
-        <f t="shared" si="11"/>
         <v>22.96</v>
       </c>
       <c r="AP90" s="5">
@@ -13905,21 +13638,18 @@
         <v>10</v>
       </c>
       <c r="AK91" s="16">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="AL91" s="12">
         <v>35</v>
       </c>
       <c r="AM91" s="16">
-        <f t="shared" si="1"/>
         <v>10.58</v>
       </c>
       <c r="AN91" s="5">
         <v>2.6</v>
       </c>
       <c r="AO91" s="5">
-        <f t="shared" si="11"/>
         <v>37.040000000000006</v>
       </c>
       <c r="AP91" s="5">
@@ -14048,21 +13778,18 @@
         <v>14</v>
       </c>
       <c r="AK92" s="16">
-        <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
       <c r="AL92" s="12">
         <v>34</v>
       </c>
       <c r="AM92" s="16">
-        <f t="shared" si="1"/>
         <v>26.204000000000001</v>
       </c>
       <c r="AN92" s="5">
         <v>3</v>
       </c>
       <c r="AO92" s="5">
-        <f>4*AN92*AN92+5</f>
         <v>41</v>
       </c>
       <c r="AP92" s="5">
@@ -14191,21 +13918,18 @@
         <v>12</v>
       </c>
       <c r="AK93" s="16">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="AL93" s="12">
         <v>36</v>
       </c>
       <c r="AM93" s="16">
-        <f t="shared" si="1"/>
         <v>14.3</v>
       </c>
       <c r="AN93" s="5">
         <v>1.9</v>
       </c>
       <c r="AO93" s="5">
-        <f t="shared" ref="AO93:AO95" si="12">4*AN93*AN93+10</f>
         <v>24.439999999999998</v>
       </c>
       <c r="AP93" s="5">
@@ -14334,21 +14058,18 @@
         <v>9</v>
       </c>
       <c r="AK94" s="16">
-        <f t="shared" si="0"/>
         <v>21.666666666666668</v>
       </c>
       <c r="AL94" s="12">
         <v>32</v>
       </c>
       <c r="AM94" s="16">
-        <f t="shared" si="1"/>
         <v>28.766666666666666</v>
       </c>
       <c r="AN94" s="5">
         <v>2.1</v>
       </c>
       <c r="AO94" s="5">
-        <f t="shared" si="12"/>
         <v>27.64</v>
       </c>
       <c r="AP94" s="5">
@@ -14477,21 +14198,18 @@
         <v>11</v>
       </c>
       <c r="AK95" s="16">
-        <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
       <c r="AL95" s="12">
         <v>39</v>
       </c>
       <c r="AM95" s="16">
-        <f t="shared" si="1"/>
         <v>12.44</v>
       </c>
       <c r="AN95" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="AO95" s="5">
-        <f t="shared" si="12"/>
         <v>14.84</v>
       </c>
       <c r="AP95" s="5">
@@ -14620,21 +14338,18 @@
         <v>13</v>
       </c>
       <c r="AK96" s="16">
-        <f t="shared" si="0"/>
         <v>12.142857142857142</v>
       </c>
       <c r="AL96" s="12">
         <v>32</v>
       </c>
       <c r="AM96" s="16">
-        <f t="shared" si="1"/>
         <v>16.957142857142856</v>
       </c>
       <c r="AN96" s="5">
         <v>1</v>
       </c>
       <c r="AO96" s="5">
-        <f>4*AN96*AN96+5</f>
         <v>9</v>
       </c>
       <c r="AP96" s="5">
@@ -14763,21 +14478,18 @@
         <v>11</v>
       </c>
       <c r="AK97" s="16">
-        <f t="shared" si="0"/>
         <v>15.6</v>
       </c>
       <c r="AL97" s="12">
         <v>38</v>
       </c>
       <c r="AM97" s="16">
-        <f t="shared" si="1"/>
         <v>21.244</v>
       </c>
       <c r="AN97" s="5">
         <v>1.5</v>
       </c>
       <c r="AO97" s="5">
-        <f>4*AN97*AN97+15</f>
         <v>24</v>
       </c>
       <c r="AP97" s="5">
@@ -14906,21 +14618,18 @@
         <v>10</v>
       </c>
       <c r="AK98" s="16">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AL98" s="12">
         <v>32</v>
       </c>
       <c r="AM98" s="16">
-        <f t="shared" si="1"/>
         <v>22.979999999999997</v>
       </c>
       <c r="AN98" s="5">
         <v>2</v>
       </c>
       <c r="AO98" s="5">
-        <f t="shared" ref="AO98:AO103" si="13">4*AN98*AN98+10</f>
         <v>26</v>
       </c>
       <c r="AP98" s="5">
@@ -15049,21 +14758,18 @@
         <v>9</v>
       </c>
       <c r="AK99" s="16">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="AL99" s="12">
         <v>32</v>
       </c>
       <c r="AM99" s="16">
-        <f t="shared" si="1"/>
         <v>32.9</v>
       </c>
       <c r="AN99" s="5">
         <v>1.7</v>
       </c>
       <c r="AO99" s="5">
-        <f t="shared" si="13"/>
         <v>21.56</v>
       </c>
       <c r="AP99" s="5">
@@ -15192,21 +14898,18 @@
         <v>14</v>
       </c>
       <c r="AK100" s="16">
-        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="AL100" s="12">
         <v>36</v>
       </c>
       <c r="AM100" s="16">
-        <f t="shared" si="1"/>
         <v>11.200000000000001</v>
       </c>
       <c r="AN100" s="5">
         <v>1.3</v>
       </c>
       <c r="AO100" s="5">
-        <f t="shared" si="13"/>
         <v>16.760000000000002</v>
       </c>
       <c r="AP100" s="5">
@@ -15335,21 +15038,18 @@
         <v>14</v>
       </c>
       <c r="AK101" s="16">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="AL101" s="12">
         <v>35</v>
       </c>
       <c r="AM101" s="16">
-        <f t="shared" si="1"/>
         <v>14.3</v>
       </c>
       <c r="AN101" s="5">
         <v>2.4</v>
       </c>
       <c r="AO101" s="5">
-        <f t="shared" si="13"/>
         <v>33.04</v>
       </c>
       <c r="AP101" s="5">
@@ -15478,21 +15178,18 @@
         <v>10</v>
       </c>
       <c r="AK102" s="16">
-        <f t="shared" si="0"/>
         <v>10.142857142857142</v>
       </c>
       <c r="AL102" s="12">
         <v>37</v>
       </c>
       <c r="AM102" s="16">
-        <f t="shared" si="1"/>
         <v>14.477142857142857</v>
       </c>
       <c r="AN102" s="5">
         <v>1.7</v>
       </c>
       <c r="AO102" s="5">
-        <f t="shared" si="13"/>
         <v>21.56</v>
       </c>
       <c r="AP102" s="5">
@@ -15621,21 +15318,18 @@
         <v>13</v>
       </c>
       <c r="AK103" s="16">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="AL103" s="12">
         <v>35</v>
       </c>
       <c r="AM103" s="16">
-        <f t="shared" si="1"/>
         <v>32.9</v>
       </c>
       <c r="AN103" s="5">
         <v>3.9</v>
       </c>
       <c r="AO103" s="5">
-        <f t="shared" si="13"/>
         <v>70.84</v>
       </c>
       <c r="AP103" s="5">
